--- a/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="576">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>
@@ -1253,6 +1253,15 @@
     <t xml:space="preserve">竜骨</t>
   </si>
   <si>
+    <t xml:space="preserve">144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepping stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">踏み石</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -1376,6 +1385,9 @@
     <t xml:space="preserve">EA 23.245</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.283</t>
+  </si>
+  <si>
     <t xml:space="preserve">null</t>
   </si>
   <si>
@@ -1728,6 +1740,9 @@
   </si>
   <si>
     <t xml:space="preserve">龙骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">垫脚石</t>
   </si>
 </sst>
 </file>
@@ -1833,10 +1848,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1852,7 +1867,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -1871,10 +1886,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -1890,10 +1905,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C6" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -1909,10 +1924,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1928,10 +1943,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -1947,10 +1962,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1966,10 +1981,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C10" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -1985,10 +2000,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2004,10 +2019,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2023,10 +2038,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2042,7 +2057,7 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C14" t="s">
         <v>42</v>
@@ -2061,10 +2076,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2080,10 +2095,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2099,10 +2114,10 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C17" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
@@ -2118,10 +2133,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -2137,10 +2152,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C19" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
@@ -2156,10 +2171,10 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
@@ -2175,10 +2190,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C21" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -2194,10 +2209,10 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C22" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D22" t="s">
         <v>64</v>
@@ -2213,10 +2228,10 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C23" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D23" t="s">
         <v>67</v>
@@ -2232,10 +2247,10 @@
         <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C24" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -2251,10 +2266,10 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C25" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D25" t="s">
         <v>73</v>
@@ -2270,10 +2285,10 @@
         <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C26" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -2289,10 +2304,10 @@
         <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -2308,10 +2323,10 @@
         <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C28" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D28" t="s">
         <v>82</v>
@@ -2327,10 +2342,10 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C29" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D29" t="s">
         <v>85</v>
@@ -2346,10 +2361,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C30" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D30" t="s">
         <v>88</v>
@@ -2365,10 +2380,10 @@
         <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C31" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D31" t="s">
         <v>91</v>
@@ -2384,10 +2399,10 @@
         <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C32" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -2403,10 +2418,10 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C33" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
@@ -2422,10 +2437,10 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C34" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D34" t="s">
         <v>100</v>
@@ -2441,10 +2456,10 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C35" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D35" t="s">
         <v>103</v>
@@ -2460,10 +2475,10 @@
         <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C36" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D36" t="s">
         <v>106</v>
@@ -2479,7 +2494,7 @@
         <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C37" t="s">
         <v>110</v>
@@ -2498,7 +2513,7 @@
         <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C38" t="s">
         <v>113</v>
@@ -2517,10 +2532,10 @@
         <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C39" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D39" t="s">
         <v>115</v>
@@ -2536,10 +2551,10 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C40" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D40" t="s">
         <v>118</v>
@@ -2555,10 +2570,10 @@
         <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C41" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D41" t="s">
         <v>121</v>
@@ -2574,10 +2589,10 @@
         <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C42" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D42" t="s">
         <v>124</v>
@@ -2593,10 +2608,10 @@
         <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C43" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D43" t="s">
         <v>127</v>
@@ -2612,10 +2627,10 @@
         <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C44" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D44" t="s">
         <v>130</v>
@@ -2631,10 +2646,10 @@
         <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C45" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D45" t="s">
         <v>133</v>
@@ -2650,7 +2665,7 @@
         <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C46" t="s">
         <v>136</v>
@@ -2669,10 +2684,10 @@
         <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D47" t="s">
         <v>138</v>
@@ -2688,10 +2703,10 @@
         <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C48" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D48" t="s">
         <v>141</v>
@@ -2707,7 +2722,7 @@
         <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C49" t="s">
         <v>110</v>
@@ -2726,10 +2741,10 @@
         <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C50" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D50" t="s">
         <v>44</v>
@@ -2745,10 +2760,10 @@
         <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C51" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D51" t="s">
         <v>147</v>
@@ -2764,10 +2779,10 @@
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C52" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D52" t="s">
         <v>150</v>
@@ -2783,10 +2798,10 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C53" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D53" t="s">
         <v>153</v>
@@ -2802,10 +2817,10 @@
         <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C54" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2821,7 +2836,7 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C55" t="s">
         <v>160</v>
@@ -2840,10 +2855,10 @@
         <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C56" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D56" t="s">
         <v>162</v>
@@ -2859,10 +2874,10 @@
         <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C57" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D57" t="s">
         <v>165</v>
@@ -2878,10 +2893,10 @@
         <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C58" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D58" t="s">
         <v>168</v>
@@ -2897,10 +2912,10 @@
         <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C59" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D59" t="s">
         <v>171</v>
@@ -2916,10 +2931,10 @@
         <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C60" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D60" t="s">
         <v>174</v>
@@ -2935,10 +2950,10 @@
         <v>176</v>
       </c>
       <c r="B61" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C61" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D61" t="s">
         <v>177</v>
@@ -2954,10 +2969,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C62" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D62" t="s">
         <v>180</v>
@@ -2973,10 +2988,10 @@
         <v>182</v>
       </c>
       <c r="B63" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C63" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D63" t="s">
         <v>183</v>
@@ -2992,10 +3007,10 @@
         <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C64" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -3011,10 +3026,10 @@
         <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C65" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D65" t="s">
         <v>189</v>
@@ -3030,10 +3045,10 @@
         <v>191</v>
       </c>
       <c r="B66" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C66" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D66" t="s">
         <v>192</v>
@@ -3049,10 +3064,10 @@
         <v>194</v>
       </c>
       <c r="B67" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C67" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
@@ -3068,10 +3083,10 @@
         <v>197</v>
       </c>
       <c r="B68" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C68" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D68" t="s">
         <v>198</v>
@@ -3087,10 +3102,10 @@
         <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C69" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D69" t="s">
         <v>201</v>
@@ -3106,10 +3121,10 @@
         <v>203</v>
       </c>
       <c r="B70" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C70" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D70" t="s">
         <v>204</v>
@@ -3125,10 +3140,10 @@
         <v>206</v>
       </c>
       <c r="B71" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C71" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D71" t="s">
         <v>207</v>
@@ -3144,10 +3159,10 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C72" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D72" t="s">
         <v>210</v>
@@ -3163,10 +3178,10 @@
         <v>212</v>
       </c>
       <c r="B73" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C73" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D73" t="s">
         <v>213</v>
@@ -3182,10 +3197,10 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C74" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D74" t="s">
         <v>216</v>
@@ -3201,10 +3216,10 @@
         <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D75" t="s">
         <v>219</v>
@@ -3220,7 +3235,7 @@
         <v>221</v>
       </c>
       <c r="B76" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C76" t="s">
         <v>223</v>
@@ -3239,10 +3254,10 @@
         <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C77" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D77" t="s">
         <v>225</v>
@@ -3258,7 +3273,7 @@
         <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C78" t="s">
         <v>229</v>
@@ -3277,10 +3292,10 @@
         <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C79" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D79" t="s">
         <v>231</v>
@@ -3296,10 +3311,10 @@
         <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C80" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D80" t="s">
         <v>234</v>
@@ -3315,7 +3330,7 @@
         <v>236</v>
       </c>
       <c r="B81" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C81" t="s">
         <v>238</v>
@@ -3334,10 +3349,10 @@
         <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C82" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D82" t="s">
         <v>240</v>
@@ -3353,10 +3368,10 @@
         <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C83" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
@@ -3372,10 +3387,10 @@
         <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C84" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D84" t="s">
         <v>245</v>
@@ -3391,7 +3406,7 @@
         <v>247</v>
       </c>
       <c r="B85" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C85" t="s">
         <v>249</v>
@@ -3410,7 +3425,7 @@
         <v>250</v>
       </c>
       <c r="B86" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C86" t="s">
         <v>110</v>
@@ -3429,10 +3444,10 @@
         <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C87" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -3448,7 +3463,7 @@
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C88" t="s">
         <v>110</v>
@@ -3467,7 +3482,7 @@
         <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C89" t="s">
         <v>110</v>
@@ -3486,7 +3501,7 @@
         <v>256</v>
       </c>
       <c r="B90" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C90" t="s">
         <v>110</v>
@@ -3505,10 +3520,10 @@
         <v>257</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C91" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D91" t="s">
         <v>258</v>
@@ -3524,10 +3539,10 @@
         <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C92" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D92" t="s">
         <v>261</v>
@@ -3543,10 +3558,10 @@
         <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C93" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D93" t="s">
         <v>264</v>
@@ -3562,10 +3577,10 @@
         <v>266</v>
       </c>
       <c r="B94" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C94" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D94" t="s">
         <v>267</v>
@@ -3581,10 +3596,10 @@
         <v>269</v>
       </c>
       <c r="B95" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D95" t="s">
         <v>270</v>
@@ -3600,10 +3615,10 @@
         <v>272</v>
       </c>
       <c r="B96" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D96" t="s">
         <v>273</v>
@@ -3619,7 +3634,7 @@
         <v>275</v>
       </c>
       <c r="B97" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C97" t="s">
         <v>277</v>
@@ -3638,10 +3653,10 @@
         <v>278</v>
       </c>
       <c r="B98" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C98" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D98" t="s">
         <v>279</v>
@@ -3657,10 +3672,10 @@
         <v>281</v>
       </c>
       <c r="B99" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C99" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D99" t="s">
         <v>279</v>
@@ -3676,10 +3691,10 @@
         <v>282</v>
       </c>
       <c r="B100" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
@@ -3695,10 +3710,10 @@
         <v>283</v>
       </c>
       <c r="B101" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D101" t="s">
         <v>100</v>
@@ -3714,10 +3729,10 @@
         <v>284</v>
       </c>
       <c r="B102" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C102" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D102" t="s">
         <v>285</v>
@@ -3733,10 +3748,10 @@
         <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C103" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D103" t="s">
         <v>288</v>
@@ -3752,10 +3767,10 @@
         <v>290</v>
       </c>
       <c r="B104" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C104" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D104" t="s">
         <v>79</v>
@@ -3771,10 +3786,10 @@
         <v>291</v>
       </c>
       <c r="B105" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C105" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D105" t="s">
         <v>292</v>
@@ -3790,7 +3805,7 @@
         <v>294</v>
       </c>
       <c r="B106" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C106" t="s">
         <v>296</v>
@@ -3809,10 +3824,10 @@
         <v>297</v>
       </c>
       <c r="B107" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C107" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D107" t="s">
         <v>298</v>
@@ -3828,7 +3843,7 @@
         <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C108" t="s">
         <v>302</v>
@@ -3847,10 +3862,10 @@
         <v>303</v>
       </c>
       <c r="B109" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C109" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D109" t="s">
         <v>79</v>
@@ -3866,10 +3881,10 @@
         <v>304</v>
       </c>
       <c r="B110" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C110" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D110" t="s">
         <v>305</v>
@@ -3885,10 +3900,10 @@
         <v>307</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C111" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3904,10 +3919,10 @@
         <v>310</v>
       </c>
       <c r="B112" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C112" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D112" t="s">
         <v>311</v>
@@ -3923,10 +3938,10 @@
         <v>313</v>
       </c>
       <c r="B113" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C113" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D113" t="s">
         <v>314</v>
@@ -3942,10 +3957,10 @@
         <v>316</v>
       </c>
       <c r="B114" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C114" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D114" t="s">
         <v>317</v>
@@ -3961,10 +3976,10 @@
         <v>319</v>
       </c>
       <c r="B115" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C115" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D115" t="s">
         <v>320</v>
@@ -3980,10 +3995,10 @@
         <v>322</v>
       </c>
       <c r="B116" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C116" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D116" t="s">
         <v>323</v>
@@ -3999,10 +4014,10 @@
         <v>325</v>
       </c>
       <c r="B117" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C117" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D117" t="s">
         <v>326</v>
@@ -4018,10 +4033,10 @@
         <v>328</v>
       </c>
       <c r="B118" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C118" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D118" t="s">
         <v>329</v>
@@ -4037,10 +4052,10 @@
         <v>331</v>
       </c>
       <c r="B119" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D119" t="s">
         <v>332</v>
@@ -4056,10 +4071,10 @@
         <v>334</v>
       </c>
       <c r="B120" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D120" t="s">
         <v>335</v>
@@ -4075,10 +4090,10 @@
         <v>337</v>
       </c>
       <c r="B121" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D121" t="s">
         <v>338</v>
@@ -4094,10 +4109,10 @@
         <v>340</v>
       </c>
       <c r="B122" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D122" t="s">
         <v>341</v>
@@ -4113,10 +4128,10 @@
         <v>343</v>
       </c>
       <c r="B123" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D123" t="s">
         <v>22</v>
@@ -4132,10 +4147,10 @@
         <v>344</v>
       </c>
       <c r="B124" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C124" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D124" t="s">
         <v>345</v>
@@ -4151,10 +4166,10 @@
         <v>347</v>
       </c>
       <c r="B125" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C125" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D125" t="s">
         <v>348</v>
@@ -4170,10 +4185,10 @@
         <v>350</v>
       </c>
       <c r="B126" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C126" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D126" t="s">
         <v>351</v>
@@ -4189,10 +4204,10 @@
         <v>353</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C127" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D127" t="s">
         <v>354</v>
@@ -4208,10 +4223,10 @@
         <v>356</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C128" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D128" t="s">
         <v>357</v>
@@ -4227,10 +4242,10 @@
         <v>359</v>
       </c>
       <c r="B129" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C129" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D129" t="s">
         <v>360</v>
@@ -4246,10 +4261,10 @@
         <v>362</v>
       </c>
       <c r="B130" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C130" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D130" t="s">
         <v>363</v>
@@ -4265,10 +4280,10 @@
         <v>365</v>
       </c>
       <c r="B131" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C131" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D131" t="s">
         <v>366</v>
@@ -4284,10 +4299,10 @@
         <v>368</v>
       </c>
       <c r="B132" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C132" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D132" t="s">
         <v>369</v>
@@ -4303,10 +4318,10 @@
         <v>371</v>
       </c>
       <c r="B133" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C133" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D133" t="s">
         <v>372</v>
@@ -4322,10 +4337,10 @@
         <v>374</v>
       </c>
       <c r="B134" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C134" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D134" t="s">
         <v>375</v>
@@ -4341,10 +4356,10 @@
         <v>377</v>
       </c>
       <c r="B135" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C135" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D135" t="s">
         <v>378</v>
@@ -4360,10 +4375,10 @@
         <v>380</v>
       </c>
       <c r="B136" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C136" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D136" t="s">
         <v>381</v>
@@ -4379,10 +4394,10 @@
         <v>383</v>
       </c>
       <c r="B137" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C137" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D137" t="s">
         <v>384</v>
@@ -4398,10 +4413,10 @@
         <v>386</v>
       </c>
       <c r="B138" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C138" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D138" t="s">
         <v>387</v>
@@ -4417,7 +4432,7 @@
         <v>389</v>
       </c>
       <c r="B139" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C139" t="s">
         <v>391</v>
@@ -4436,10 +4451,10 @@
         <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C140" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D140" t="s">
         <v>393</v>
@@ -4455,10 +4470,10 @@
         <v>395</v>
       </c>
       <c r="B141" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C141" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D141" t="s">
         <v>396</v>
@@ -4474,10 +4489,10 @@
         <v>398</v>
       </c>
       <c r="B142" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C142" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D142" t="s">
         <v>399</v>
@@ -4493,10 +4508,10 @@
         <v>401</v>
       </c>
       <c r="B143" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C143" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D143" t="s">
         <v>402</v>
@@ -4512,10 +4527,10 @@
         <v>404</v>
       </c>
       <c r="B144" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C144" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D144" t="s">
         <v>405</v>
@@ -4531,10 +4546,10 @@
         <v>407</v>
       </c>
       <c r="B145" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C145" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D145" t="s">
         <v>408</v>
@@ -4550,10 +4565,10 @@
         <v>410</v>
       </c>
       <c r="B146" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C146" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D146" t="s">
         <v>159</v>
@@ -4563,6 +4578,25 @@
       </c>
       <c r="G146"/>
       <c r="H146"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>412</v>
+      </c>
+      <c r="B147" t="s">
+        <v>456</v>
+      </c>
+      <c r="C147" t="s">
+        <v>575</v>
+      </c>
+      <c r="D147" t="s">
+        <v>413</v>
+      </c>
+      <c r="E147" t="s">
+        <v>414</v>
+      </c>
+      <c r="G147"/>
+      <c r="H147"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>
